--- a/site v2/tableur-reglages-kart-v2.xlsx
+++ b/site v2/tableur-reglages-kart-v2.xlsx
@@ -627,14 +627,14 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Clem Kart Racing — note le QUOI. Le guide explique le POURQUOI.</t>
+          <t xml:space="preserve">  Clem Kart Racing : note le QUOI. Le guide explique le POURQUOI.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Comment l'utiliser — 3 étapes</t>
+          <t xml:space="preserve">  Comment l'utiliser : 3 étapes</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Comprendre le POURQUOI derriere chaque reglage  -&gt;  Guide « Comprendre comment rouler plus vite »</t>
+          <t>Comprendre le POURQUOI derrière chaque réglage  -&gt;  Guide « Comprendre comment rouler plus vite »</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PNEUS — pression (vue de dessus du kart · Δ calculé auto)</t>
+          <t xml:space="preserve">  PNEUS : pression (vue de dessus du kart · Δ calculé auto)</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PNEUS — pression (vue de dessus du kart · Δ calculé auto)</t>
+          <t xml:space="preserve">  PNEUS : pression (vue de dessus du kart · Δ calculé auto)</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PNEUS — pression (vue de dessus du kart · Δ calculé auto)</t>
+          <t xml:space="preserve">  PNEUS : pression (vue de dessus du kart · Δ calculé auto)</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PNEUS — pression (vue de dessus du kart · Δ calculé auto)</t>
+          <t xml:space="preserve">  PNEUS : pression (vue de dessus du kart · Δ calculé auto)</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PNEUS — pression (vue de dessus du kart · Δ calculé auto)</t>
+          <t xml:space="preserve">  PNEUS : pression (vue de dessus du kart · Δ calculé auto)</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>Comprendre le POURQUOI derriere chaque reglage  -&gt;  Guide « Comprendre comment rouler plus vite »</t>
+          <t>Comprendre le POURQUOI derrière chaque réglage  -&gt;  Guide « Comprendre comment rouler plus vite »</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CHÂSSIS — géométrie</t>
+          <t xml:space="preserve">  CHÂSSIS : géométrie</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CHÂSSIS — grip &amp; rigidité</t>
+          <t xml:space="preserve">  CHÂSSIS : grip &amp; rigidité</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Comprendre le POURQUOI derriere chaque reglage  -&gt;  Guide « Comprendre comment rouler plus vite »</t>
+          <t>Comprendre le POURQUOI derrière chaque réglage  -&gt;  Guide « Comprendre comment rouler plus vite »</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3849,14 +3849,14 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Guide digital · 32 pages · 14,99 €  ·  Garantie 7 jours, satisfait ou remboursé.</t>
+          <t xml:space="preserve">   Guide digital · 59 pages · 16,99 €  ·  Garantie 7 jours, satisfait ou remboursé.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>OBTENIR LE GUIDE « Comprendre comment rouler plus vite »   —   14,99 €   ➜</t>
+          <t>OBTENIR LE GUIDE « Comprendre comment rouler plus vite »   ·   16,99 €   ➜</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Pressions cibles (point de départ — à adapter à ta marque)</t>
+          <t xml:space="preserve">  Pressions cibles (point de départ, à adapter à ta marque)</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Checklist pluie — dans l'ordre, avant de rouler</t>
+          <t xml:space="preserve">  Checklist pluie : dans l'ordre, avant de rouler</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Comprendre le POURQUOI derriere chaque reglage  -&gt;  Guide « Comprendre comment rouler plus vite »</t>
+          <t>Comprendre le POURQUOI derrière chaque réglage  -&gt;  Guide « Comprendre comment rouler plus vite »</t>
         </is>
       </c>
     </row>

--- a/site v2/tableur-reglages-kart-v2.xlsx
+++ b/site v2/tableur-reglages-kart-v2.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="🏁 Accueil" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="📓 Journal" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="🔧 Guide des réglages" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="🩺 Diagnostic express" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="☔ Pressions &amp; pluie" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Accueil" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Journal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Guide des réglages" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Diagnostic express" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pressions et pluie" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3849,14 +3849,14 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Guide digital · 59 pages · 16,99 €  ·  Garantie 7 jours, satisfait ou remboursé.</t>
+          <t xml:space="preserve">   Guide PDF · 59 pages · Garantie 7 jours, en plus de tes droits légaux.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>OBTENIR LE GUIDE « Comprendre comment rouler plus vite »   ·   16,99 €   ➜</t>
+          <t>VOIR LE GUIDE « Comprendre comment rouler plus vite »   →</t>
         </is>
       </c>
     </row>
